--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.22778266086141</v>
+        <v>6.374514682389979</v>
       </c>
       <c r="D2" t="n">
-        <v>3.197397976020392</v>
+        <v>0.5195771711033137</v>
       </c>
       <c r="E2" t="n">
-        <v>24.52903906503597</v>
+        <v>3.985968848068345</v>
       </c>
       <c r="F2" t="n">
-        <v>28.83866904746284</v>
+        <v>4.686283720212712</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>104.4264429604632</v>
+        <v>16.96929698107526</v>
       </c>
       <c r="D3" t="n">
-        <v>84.23854270374115</v>
+        <v>13.68876318935794</v>
       </c>
       <c r="E3" t="n">
-        <v>24.52903906503597</v>
+        <v>3.985968848068345</v>
       </c>
       <c r="F3" t="n">
-        <v>28.83866904746284</v>
+        <v>4.686283720212712</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>61.74193370084887</v>
+        <v>10.03306422638794</v>
       </c>
       <c r="D4" t="n">
-        <v>37.59321747336878</v>
+        <v>6.108897839422427</v>
       </c>
       <c r="E4" t="n">
-        <v>24.52903906503597</v>
+        <v>3.985968848068345</v>
       </c>
       <c r="F4" t="n">
-        <v>28.83866904746284</v>
+        <v>4.686283720212712</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>51.59509095756641</v>
+        <v>8.384202280604541</v>
       </c>
       <c r="D5" t="n">
-        <v>36.8001358693144</v>
+        <v>5.980022078763589</v>
       </c>
       <c r="E5" t="n">
-        <v>24.52903906503597</v>
+        <v>3.985968848068345</v>
       </c>
       <c r="F5" t="n">
-        <v>28.83866904746284</v>
+        <v>4.686283720212712</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
